--- a/Github_Excel004.xlsx
+++ b/Github_Excel004.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LinhLT\Job\02.Server_GIT\8352\8352_repoGithub001\A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\リンLinhLT\Documents\Local_copy\8352\8352_Project033 1\branches01\5.2.1_8352_repoGithub001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3587D007-030C-4B41-A90D-2D611DB2FD7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6D86C2-44E1-48DA-A8CA-58F6A21BE585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
   <si>
-    <t>A1</t>
-  </si>
-  <si>
     <t>A2</t>
   </si>
   <si>
@@ -166,6 +163,9 @@
   </si>
   <si>
     <t>C26_11</t>
+  </si>
+  <si>
+    <t>A1_999</t>
   </si>
 </sst>
 </file>
@@ -500,217 +500,217 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="C25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
